--- a/outputs/48643.xlsx
+++ b/outputs/48643.xlsx
@@ -200,104 +200,108 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="19" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="19" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="19" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="19" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -584,832 +588,832 @@
   <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="12.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="12" t="n">
         <v>2020</v>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="13" t="n">
         <v>1200</v>
       </c>
-      <c r="C2" s="13" t="n">
+      <c r="C2" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="15" t="n">
         <v>0.021</v>
       </c>
-      <c r="E2" s="15" t="n">
+      <c r="E2" s="16" t="n">
         <f aca="false">B2*C2</f>
         <v>72</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <f aca="false">(1+C2)*B2</f>
         <v>1272</v>
       </c>
-      <c r="H2" s="17" t="n">
-        <f aca="false">(B2)*(1+C2)</f>
+      <c r="H2" s="18" t="n">
+        <f aca="false">B2*(1+C2)</f>
         <v>1272</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="12" t="n">
         <v>2021</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="13" t="n">
         <v>1500</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="14" t="n">
         <v>0.05</v>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="15" t="n">
         <v>0.022</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="16" t="n">
         <f aca="false">B3*C3</f>
         <v>75</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <f aca="false">(1+C3)*B3</f>
         <v>1575</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="19" t="n">
         <f aca="false">(H2+B3)*(1+C3)</f>
         <v>2910.6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="12" t="n">
         <v>2022</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="13" t="n">
         <v>1500</v>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="14" t="n">
         <v>0.07</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>0.022</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <f aca="false">B4*C4</f>
         <v>105</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <f aca="false">(1+C4)*B4</f>
         <v>1605</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="19" t="n">
         <f aca="false">(H3+B4)*(1+C4)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>2023</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15" t="n">
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16" t="n">
         <f aca="false">B5*C5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <f aca="false">(1+C5)*B5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="19" t="n">
         <f aca="false">(H4+B5)*(1+C5)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="12" t="n">
         <v>2024</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15" t="n">
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16" t="n">
         <f aca="false">B6*C6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <f aca="false">(1+C6)*B6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="19" t="n">
         <f aca="false">(H5+B6)*(1+C6)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="12" t="n">
         <v>2025</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="15" t="n">
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16" t="n">
         <f aca="false">B7*C7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <f aca="false">(1+C7)*B7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="19" t="n">
         <f aca="false">(H6+B7)*(1+C7)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="12" t="n">
         <v>2026</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15" t="n">
+      <c r="B8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16" t="n">
         <f aca="false">B8*C8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <f aca="false">(1+C8)*B8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="19" t="n">
         <f aca="false">(H7+B8)*(1+C8)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="12" t="n">
         <v>2027</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="15" t="n">
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16" t="n">
         <f aca="false">B9*C9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <f aca="false">(1+C9)*B9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="19" t="n">
         <f aca="false">(H8+B9)*(1+C9)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="12" t="n">
         <v>2028</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="15" t="n">
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16" t="n">
         <f aca="false">B10*C10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <f aca="false">(1+C10)*B10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="19" t="n">
         <f aca="false">(H9+B10)*(1+C10)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <v>2029</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15" t="n">
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16" t="n">
         <f aca="false">B11*C11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <f aca="false">(1+C11)*B11</f>
         <v>0</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="19" t="n">
         <f aca="false">(H10+B11)*(1+C11)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="12" t="n">
         <v>2030</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="15" t="n">
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16" t="n">
         <f aca="false">B12*C12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <f aca="false">(1+C12)*B12</f>
         <v>0</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <f aca="false">(H11+B12)*(1+C12)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="12" t="n">
         <v>2031</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="15" t="n">
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16" t="n">
         <f aca="false">B13*C13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <f aca="false">(1+C13)*B13</f>
         <v>0</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="19" t="n">
         <f aca="false">(H12+B13)*(1+C13)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="12" t="n">
         <v>2032</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="15" t="n">
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16" t="n">
         <f aca="false">B14*C14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <f aca="false">(1+C14)*B14</f>
         <v>0</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="19" t="n">
         <f aca="false">(H13+B14)*(1+C14)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="12" t="n">
         <v>2033</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="15" t="n">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="16" t="n">
         <f aca="false">B15*C15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <f aca="false">(1+C15)*B15</f>
         <v>0</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="19" t="n">
         <f aca="false">(H14+B15)*(1+C15)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="12" t="n">
         <v>2034</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="15" t="n">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16" t="n">
         <f aca="false">B16*C16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <f aca="false">(1+C16)*B16</f>
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="19" t="n">
         <f aca="false">(H15+B16)*(1+C16)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="12" t="n">
         <v>2035</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="15" t="n">
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="16" t="n">
         <f aca="false">B17*C17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <f aca="false">(1+C17)*B17</f>
         <v>0</v>
       </c>
-      <c r="H17" s="18" t="n">
+      <c r="H17" s="19" t="n">
         <f aca="false">(H16+B17)*(1+C17)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="12" t="n">
         <v>2036</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="15" t="n">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16" t="n">
         <f aca="false">B18*C18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <f aca="false">(1+C18)*B18</f>
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
+      <c r="H18" s="19" t="n">
         <f aca="false">(H17+B18)*(1+C18)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="12" t="n">
         <v>2037</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="15" t="n">
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="16" t="n">
         <f aca="false">B19*C19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <f aca="false">(1+C19)*B19</f>
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
+      <c r="H19" s="19" t="n">
         <f aca="false">(H18+B19)*(1+C19)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="12" t="n">
         <v>2038</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="15" t="n">
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="16" t="n">
         <f aca="false">B20*C20</f>
         <v>0</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <f aca="false">(1+C20)*B20</f>
         <v>0</v>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="H20" s="19" t="n">
         <f aca="false">(H19+B20)*(1+C20)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="12" t="n">
         <v>2039</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="15" t="n">
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="16" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <f aca="false">(1+C21)*B21</f>
         <v>0</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="19" t="n">
         <f aca="false">(H20+B21)*(1+C21)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="12" t="n">
         <v>2040</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="15" t="n">
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <f aca="false">(1+C22)*B22</f>
         <v>0</v>
       </c>
-      <c r="H22" s="18" t="n">
+      <c r="H22" s="19" t="n">
         <f aca="false">(H21+B22)*(1+C22)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="12" t="n">
         <v>2041</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="15" t="n">
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16" t="n">
         <f aca="false">B23*C23</f>
         <v>0</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <f aca="false">(1+C23)*B23</f>
         <v>0</v>
       </c>
-      <c r="H23" s="18" t="n">
+      <c r="H23" s="19" t="n">
         <f aca="false">(H22+B23)*(1+C23)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="12" t="n">
         <v>2042</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="15" t="n">
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="16" t="n">
         <f aca="false">B24*C24</f>
         <v>0</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <f aca="false">(1+C24)*B24</f>
         <v>0</v>
       </c>
-      <c r="H24" s="18" t="n">
+      <c r="H24" s="19" t="n">
         <f aca="false">(H23+B24)*(1+C24)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="12" t="n">
         <v>2043</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="15" t="n">
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="16" t="n">
         <f aca="false">B25*C25</f>
         <v>0</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="17" t="n">
         <f aca="false">(1+C25)*B25</f>
         <v>0</v>
       </c>
-      <c r="H25" s="18" t="n">
+      <c r="H25" s="19" t="n">
         <f aca="false">(H24+B25)*(1+C25)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="12" t="n">
         <v>2044</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15" t="n">
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16" t="n">
         <f aca="false">B26*C26</f>
         <v>0</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <f aca="false">(1+C26)*B26</f>
         <v>0</v>
       </c>
-      <c r="H26" s="18" t="n">
+      <c r="H26" s="19" t="n">
         <f aca="false">(H25+B26)*(1+C26)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="12" t="n">
         <v>2045</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="15" t="n">
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16" t="n">
         <f aca="false">B27*C27</f>
         <v>0</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <f aca="false">(1+C27)*B27</f>
         <v>0</v>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="H27" s="19" t="n">
         <f aca="false">(H26+B27)*(1+C27)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="12" t="n">
         <v>2046</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="15" t="n">
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16" t="n">
         <f aca="false">B28*C28</f>
         <v>0</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <f aca="false">(1+C28)*B28</f>
         <v>0</v>
       </c>
-      <c r="H28" s="18" t="n">
+      <c r="H28" s="19" t="n">
         <f aca="false">(H27+B28)*(1+C28)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="12" t="n">
         <v>2047</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="15" t="n">
+      <c r="B29" s="13"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16" t="n">
         <f aca="false">B29*C29</f>
         <v>0</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <f aca="false">(1+C29)*B29</f>
         <v>0</v>
       </c>
-      <c r="H29" s="18" t="n">
+      <c r="H29" s="19" t="n">
         <f aca="false">(H28+B29)*(1+C29)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="12" t="n">
         <v>2048</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="15" t="n">
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16" t="n">
         <f aca="false">B30*C30</f>
         <v>0</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="17" t="n">
         <f aca="false">(1+C30)*B30</f>
         <v>0</v>
       </c>
-      <c r="H30" s="18" t="n">
+      <c r="H30" s="19" t="n">
         <f aca="false">(H29+B30)*(1+C30)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="12" t="n">
         <v>2049</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="15" t="n">
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16" t="n">
         <f aca="false">B31*C31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <f aca="false">(1+C31)*B31</f>
         <v>0</v>
       </c>
-      <c r="H31" s="18" t="n">
+      <c r="H31" s="19" t="n">
         <f aca="false">(H30+B31)*(1+C31)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="12" t="n">
         <v>2050</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="15" t="n">
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="16" t="n">
         <f aca="false">B32*C32</f>
         <v>0</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <f aca="false">(1+C32)*B32</f>
         <v>0</v>
       </c>
-      <c r="H32" s="18" t="n">
+      <c r="H32" s="19" t="n">
         <f aca="false">(H31+B32)*(1+C32)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="12" t="n">
         <v>2051</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="15" t="n">
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="16" t="n">
         <f aca="false">B33*C33</f>
         <v>0</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <f aca="false">(1+C33)*B33</f>
         <v>0</v>
       </c>
-      <c r="H33" s="18" t="n">
+      <c r="H33" s="19" t="n">
         <f aca="false">(H32+B33)*(1+C33)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="12" t="n">
         <v>2052</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="15" t="n">
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="16" t="n">
         <f aca="false">B34*C34</f>
         <v>0</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="17" t="n">
         <f aca="false">(1+C34)*B34</f>
         <v>0</v>
       </c>
-      <c r="H34" s="18" t="n">
+      <c r="H34" s="19" t="n">
         <f aca="false">(H33+B34)*(1+C34)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="12" t="n">
         <v>2053</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="15" t="n">
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="16" t="n">
         <f aca="false">B35*C35</f>
         <v>0</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="17" t="n">
         <f aca="false">(1+C35)*B35</f>
         <v>0</v>
       </c>
-      <c r="H35" s="18" t="n">
+      <c r="H35" s="19" t="n">
         <f aca="false">(H34+B35)*(1+C35)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="12" t="n">
         <v>2054</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15" t="n">
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="16" t="n">
         <f aca="false">B36*C36</f>
         <v>0</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <f aca="false">(1+C36)*B36</f>
         <v>0</v>
       </c>
-      <c r="H36" s="18" t="n">
+      <c r="H36" s="19" t="n">
         <f aca="false">(H35+B36)*(1+C36)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="12" t="n">
         <v>2055</v>
       </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="15" t="n">
+      <c r="B37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="16" t="n">
         <f aca="false">B37*C37</f>
         <v>0</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <f aca="false">(1+C37)*B37</f>
         <v>0</v>
       </c>
-      <c r="H37" s="18" t="n">
+      <c r="H37" s="19" t="n">
         <f aca="false">(H36+B37)*(1+C37)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11" t="n">
+      <c r="A38" s="12" t="n">
         <v>2056</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="15" t="n">
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="16" t="n">
         <f aca="false">B38*C38</f>
         <v>0</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="17" t="n">
         <f aca="false">(1+C38)*B38</f>
         <v>0</v>
       </c>
-      <c r="H38" s="18" t="n">
+      <c r="H38" s="19" t="n">
         <f aca="false">(H37+B38)*(1+C38)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11" t="n">
+      <c r="A39" s="12" t="n">
         <v>2057</v>
       </c>
-      <c r="B39" s="12"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="15" t="n">
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="16" t="n">
         <f aca="false">B39*C39</f>
         <v>0</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="F39" s="17" t="n">
         <f aca="false">(1+C39)*B39</f>
         <v>0</v>
       </c>
-      <c r="H39" s="18" t="n">
+      <c r="H39" s="19" t="n">
         <f aca="false">(H38+B39)*(1+C39)</f>
         <v>4719.342</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="n">
+      <c r="A40" s="20" t="n">
         <v>2058</v>
       </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="23" t="n">
+      <c r="B40" s="21"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="24" t="n">
         <f aca="false">B40*C40</f>
         <v>0</v>
       </c>
-      <c r="F40" s="24" t="n">
+      <c r="F40" s="25" t="n">
         <f aca="false">(1+C40)*B40</f>
         <v>0</v>
       </c>
-      <c r="H40" s="18" t="n">
+      <c r="H40" s="19" t="n">
         <f aca="false">(H39+B40)*(1+C40)</f>
         <v>4719.342</v>
       </c>

--- a/outputs/48643.xlsx
+++ b/outputs/48643.xlsx
@@ -47,12 +47,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[$€-413]\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -195,12 +194,9 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -209,15 +205,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -229,11 +225,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -249,59 +245,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -597,7 +585,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -620,7 +608,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="n">
         <v>2020</v>
       </c>
@@ -641,12 +629,12 @@
         <f aca="false">(1+C2)*B2</f>
         <v>1272</v>
       </c>
-      <c r="H2" s="18" t="n">
-        <f aca="false">B2*(1+C2)</f>
+      <c r="H2" s="2" t="n">
+        <f aca="false">F2</f>
         <v>1272</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="n">
         <v>2021</v>
       </c>
@@ -667,12 +655,12 @@
         <f aca="false">(1+C3)*B3</f>
         <v>1575</v>
       </c>
-      <c r="H3" s="19" t="n">
-        <f aca="false">(H2+B3)*(1+C3)</f>
-        <v>2910.6</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H3" s="2" t="n">
+        <f aca="false">IF(F3=0,0,H2+F3)</f>
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="n">
         <v>2022</v>
       </c>
@@ -693,12 +681,12 @@
         <f aca="false">(1+C4)*B4</f>
         <v>1605</v>
       </c>
-      <c r="H4" s="19" t="n">
-        <f aca="false">(H3+B4)*(1+C4)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H4" s="2" t="n">
+        <f aca="false">IF(F4=0,0,H3+F4)</f>
+        <v>4452</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="n">
         <v>2023</v>
       </c>
@@ -713,12 +701,12 @@
         <f aca="false">(1+C5)*B5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="19" t="n">
-        <f aca="false">(H4+B5)*(1+C5)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H5" s="1" t="n">
+        <f aca="false">IF(F5=0,0,H4+F5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="n">
         <v>2024</v>
       </c>
@@ -733,12 +721,12 @@
         <f aca="false">(1+C6)*B6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="19" t="n">
-        <f aca="false">(H5+B6)*(1+C6)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="1" t="n">
+        <f aca="false">IF(F6=0,0,H5+F6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="n">
         <v>2025</v>
       </c>
@@ -753,12 +741,12 @@
         <f aca="false">(1+C7)*B7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="19" t="n">
-        <f aca="false">(H6+B7)*(1+C7)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="1" t="n">
+        <f aca="false">IF(F7=0,0,H6+F7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="n">
         <v>2026</v>
       </c>
@@ -773,12 +761,12 @@
         <f aca="false">(1+C8)*B8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="19" t="n">
-        <f aca="false">(H7+B8)*(1+C8)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="1" t="n">
+        <f aca="false">IF(F8=0,0,H7+F8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="n">
         <v>2027</v>
       </c>
@@ -793,12 +781,12 @@
         <f aca="false">(1+C9)*B9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="19" t="n">
-        <f aca="false">(H8+B9)*(1+C9)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H9" s="1" t="n">
+        <f aca="false">IF(F9=0,0,H8+F9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
         <v>2028</v>
       </c>
@@ -813,12 +801,12 @@
         <f aca="false">(1+C10)*B10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="19" t="n">
-        <f aca="false">(H9+B10)*(1+C10)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="1" t="n">
+        <f aca="false">IF(F10=0,0,H9+F10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="n">
         <v>2029</v>
       </c>
@@ -833,12 +821,12 @@
         <f aca="false">(1+C11)*B11</f>
         <v>0</v>
       </c>
-      <c r="H11" s="19" t="n">
-        <f aca="false">(H10+B11)*(1+C11)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="1" t="n">
+        <f aca="false">IF(F11=0,0,H10+F11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="n">
         <v>2030</v>
       </c>
@@ -853,12 +841,12 @@
         <f aca="false">(1+C12)*B12</f>
         <v>0</v>
       </c>
-      <c r="H12" s="19" t="n">
-        <f aca="false">(H11+B12)*(1+C12)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="1" t="n">
+        <f aca="false">IF(F12=0,0,H11+F12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="n">
         <v>2031</v>
       </c>
@@ -873,12 +861,12 @@
         <f aca="false">(1+C13)*B13</f>
         <v>0</v>
       </c>
-      <c r="H13" s="19" t="n">
-        <f aca="false">(H12+B13)*(1+C13)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="1" t="n">
+        <f aca="false">IF(F13=0,0,H12+F13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="n">
         <v>2032</v>
       </c>
@@ -893,12 +881,12 @@
         <f aca="false">(1+C14)*B14</f>
         <v>0</v>
       </c>
-      <c r="H14" s="19" t="n">
-        <f aca="false">(H13+B14)*(1+C14)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="1" t="n">
+        <f aca="false">IF(F14=0,0,H13+F14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="n">
         <v>2033</v>
       </c>
@@ -913,12 +901,12 @@
         <f aca="false">(1+C15)*B15</f>
         <v>0</v>
       </c>
-      <c r="H15" s="19" t="n">
-        <f aca="false">(H14+B15)*(1+C15)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="1" t="n">
+        <f aca="false">IF(F15=0,0,H14+F15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="n">
         <v>2034</v>
       </c>
@@ -933,12 +921,12 @@
         <f aca="false">(1+C16)*B16</f>
         <v>0</v>
       </c>
-      <c r="H16" s="19" t="n">
-        <f aca="false">(H15+B16)*(1+C16)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="1" t="n">
+        <f aca="false">IF(F16=0,0,H15+F16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="n">
         <v>2035</v>
       </c>
@@ -953,12 +941,12 @@
         <f aca="false">(1+C17)*B17</f>
         <v>0</v>
       </c>
-      <c r="H17" s="19" t="n">
-        <f aca="false">(H16+B17)*(1+C17)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="1" t="n">
+        <f aca="false">IF(F17=0,0,H16+F17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="n">
         <v>2036</v>
       </c>
@@ -973,12 +961,12 @@
         <f aca="false">(1+C18)*B18</f>
         <v>0</v>
       </c>
-      <c r="H18" s="19" t="n">
-        <f aca="false">(H17+B18)*(1+C18)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="1" t="n">
+        <f aca="false">IF(F18=0,0,H17+F18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="n">
         <v>2037</v>
       </c>
@@ -993,12 +981,12 @@
         <f aca="false">(1+C19)*B19</f>
         <v>0</v>
       </c>
-      <c r="H19" s="19" t="n">
-        <f aca="false">(H18+B19)*(1+C19)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="1" t="n">
+        <f aca="false">IF(F19=0,0,H18+F19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="n">
         <v>2038</v>
       </c>
@@ -1013,12 +1001,12 @@
         <f aca="false">(1+C20)*B20</f>
         <v>0</v>
       </c>
-      <c r="H20" s="19" t="n">
-        <f aca="false">(H19+B20)*(1+C20)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="1" t="n">
+        <f aca="false">IF(F20=0,0,H19+F20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
         <v>2039</v>
       </c>
@@ -1033,12 +1021,12 @@
         <f aca="false">(1+C21)*B21</f>
         <v>0</v>
       </c>
-      <c r="H21" s="19" t="n">
-        <f aca="false">(H20+B21)*(1+C21)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="1" t="n">
+        <f aca="false">IF(F21=0,0,H20+F21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="n">
         <v>2040</v>
       </c>
@@ -1053,12 +1041,12 @@
         <f aca="false">(1+C22)*B22</f>
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <f aca="false">(H21+B22)*(1+C22)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="1" t="n">
+        <f aca="false">IF(F22=0,0,H21+F22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="n">
         <v>2041</v>
       </c>
@@ -1073,12 +1061,12 @@
         <f aca="false">(1+C23)*B23</f>
         <v>0</v>
       </c>
-      <c r="H23" s="19" t="n">
-        <f aca="false">(H22+B23)*(1+C23)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="1" t="n">
+        <f aca="false">IF(F23=0,0,H22+F23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="n">
         <v>2042</v>
       </c>
@@ -1093,12 +1081,12 @@
         <f aca="false">(1+C24)*B24</f>
         <v>0</v>
       </c>
-      <c r="H24" s="19" t="n">
-        <f aca="false">(H23+B24)*(1+C24)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="1" t="n">
+        <f aca="false">IF(F24=0,0,H23+F24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="n">
         <v>2043</v>
       </c>
@@ -1113,12 +1101,12 @@
         <f aca="false">(1+C25)*B25</f>
         <v>0</v>
       </c>
-      <c r="H25" s="19" t="n">
-        <f aca="false">(H24+B25)*(1+C25)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="1" t="n">
+        <f aca="false">IF(F25=0,0,H24+F25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="n">
         <v>2044</v>
       </c>
@@ -1133,12 +1121,12 @@
         <f aca="false">(1+C26)*B26</f>
         <v>0</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <f aca="false">(H25+B26)*(1+C26)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="1" t="n">
+        <f aca="false">IF(F26=0,0,H25+F26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="n">
         <v>2045</v>
       </c>
@@ -1153,12 +1141,12 @@
         <f aca="false">(1+C27)*B27</f>
         <v>0</v>
       </c>
-      <c r="H27" s="19" t="n">
-        <f aca="false">(H26+B27)*(1+C27)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="1" t="n">
+        <f aca="false">IF(F27=0,0,H26+F27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="n">
         <v>2046</v>
       </c>
@@ -1173,12 +1161,12 @@
         <f aca="false">(1+C28)*B28</f>
         <v>0</v>
       </c>
-      <c r="H28" s="19" t="n">
-        <f aca="false">(H27+B28)*(1+C28)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="1" t="n">
+        <f aca="false">IF(F28=0,0,H27+F28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="n">
         <v>2047</v>
       </c>
@@ -1193,12 +1181,12 @@
         <f aca="false">(1+C29)*B29</f>
         <v>0</v>
       </c>
-      <c r="H29" s="19" t="n">
-        <f aca="false">(H28+B29)*(1+C29)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="1" t="n">
+        <f aca="false">IF(F29=0,0,H28+F29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="n">
         <v>2048</v>
       </c>
@@ -1213,12 +1201,12 @@
         <f aca="false">(1+C30)*B30</f>
         <v>0</v>
       </c>
-      <c r="H30" s="19" t="n">
-        <f aca="false">(H29+B30)*(1+C30)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="1" t="n">
+        <f aca="false">IF(F30=0,0,H29+F30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="n">
         <v>2049</v>
       </c>
@@ -1233,12 +1221,12 @@
         <f aca="false">(1+C31)*B31</f>
         <v>0</v>
       </c>
-      <c r="H31" s="19" t="n">
-        <f aca="false">(H30+B31)*(1+C31)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="1" t="n">
+        <f aca="false">IF(F31=0,0,H30+F31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="n">
         <v>2050</v>
       </c>
@@ -1253,12 +1241,12 @@
         <f aca="false">(1+C32)*B32</f>
         <v>0</v>
       </c>
-      <c r="H32" s="19" t="n">
-        <f aca="false">(H31+B32)*(1+C32)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="1" t="n">
+        <f aca="false">IF(F32=0,0,H31+F32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="n">
         <v>2051</v>
       </c>
@@ -1273,12 +1261,12 @@
         <f aca="false">(1+C33)*B33</f>
         <v>0</v>
       </c>
-      <c r="H33" s="19" t="n">
-        <f aca="false">(H32+B33)*(1+C33)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="1" t="n">
+        <f aca="false">IF(F33=0,0,H32+F33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="n">
         <v>2052</v>
       </c>
@@ -1293,12 +1281,12 @@
         <f aca="false">(1+C34)*B34</f>
         <v>0</v>
       </c>
-      <c r="H34" s="19" t="n">
-        <f aca="false">(H33+B34)*(1+C34)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="1" t="n">
+        <f aca="false">IF(F34=0,0,H33+F34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="n">
         <v>2053</v>
       </c>
@@ -1313,12 +1301,12 @@
         <f aca="false">(1+C35)*B35</f>
         <v>0</v>
       </c>
-      <c r="H35" s="19" t="n">
-        <f aca="false">(H34+B35)*(1+C35)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="1" t="n">
+        <f aca="false">IF(F35=0,0,H34+F35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="n">
         <v>2054</v>
       </c>
@@ -1333,12 +1321,12 @@
         <f aca="false">(1+C36)*B36</f>
         <v>0</v>
       </c>
-      <c r="H36" s="19" t="n">
-        <f aca="false">(H35+B36)*(1+C36)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="1" t="n">
+        <f aca="false">IF(F36=0,0,H35+F36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="n">
         <v>2055</v>
       </c>
@@ -1353,12 +1341,12 @@
         <f aca="false">(1+C37)*B37</f>
         <v>0</v>
       </c>
-      <c r="H37" s="19" t="n">
-        <f aca="false">(H36+B37)*(1+C37)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="1" t="n">
+        <f aca="false">IF(F37=0,0,H36+F37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="n">
         <v>2056</v>
       </c>
@@ -1373,12 +1361,12 @@
         <f aca="false">(1+C38)*B38</f>
         <v>0</v>
       </c>
-      <c r="H38" s="19" t="n">
-        <f aca="false">(H37+B38)*(1+C38)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="1" t="n">
+        <f aca="false">IF(F38=0,0,H37+F38)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="n">
         <v>2057</v>
       </c>
@@ -1393,29 +1381,29 @@
         <f aca="false">(1+C39)*B39</f>
         <v>0</v>
       </c>
-      <c r="H39" s="19" t="n">
-        <f aca="false">(H38+B39)*(1+C39)</f>
-        <v>4719.342</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="n">
+      <c r="H39" s="1" t="n">
+        <f aca="false">IF(F39=0,0,H38+F39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="n">
         <v>2058</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="24" t="n">
+      <c r="B40" s="19"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="22" t="n">
         <f aca="false">B40*C40</f>
         <v>0</v>
       </c>
-      <c r="F40" s="25" t="n">
+      <c r="F40" s="23" t="n">
         <f aca="false">(1+C40)*B40</f>
         <v>0</v>
       </c>
-      <c r="H40" s="19" t="n">
-        <f aca="false">(H39+B40)*(1+C40)</f>
-        <v>4719.342</v>
+      <c r="H40" s="1" t="n">
+        <f aca="false">IF(F40=0,0,H39+F40)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
